--- a/Configs/GameConfig/Datas/商店表.xlsx
+++ b/Configs/GameConfig/Datas/商店表.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,26 +27,26 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
   <si>
     <t>##var</t>
   </si>
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>i</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>d</t>
     </r>
@@ -60,19 +60,19 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>d</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>esc</t>
     </r>
@@ -116,19 +116,19 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>这是i</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color rgb="FF006100"/>
         <rFont val="等线"/>
         <charset val="134"/>
+        <color rgb="FF006100"/>
+        <sz val="11"/>
       </rPr>
       <t>d</t>
     </r>
@@ -149,58 +149,139 @@
     <t>主奖励</t>
   </si>
   <si>
-    <t>奖励1</t>
+    <t>1</t>
+  </si>
+  <si>
+    <t>奖励13</t>
+  </si>
+  <si>
+    <t>奖励12</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>10001</t>
   </si>
   <si>
     <t>10001;10002</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>奖励2</t>
   </si>
   <si>
+    <t>10002</t>
+  </si>
+  <si>
     <t>10001;10003</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>奖励3</t>
   </si>
   <si>
+    <t>奖励3321321</t>
+  </si>
+  <si>
+    <t>10003</t>
+  </si>
+  <si>
     <t>10001;10004</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>奖励4</t>
   </si>
   <si>
+    <t>奖励43321321</t>
+  </si>
+  <si>
+    <t>10004</t>
+  </si>
+  <si>
     <t>10001;10005</t>
   </si>
   <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>奖励5</t>
   </si>
   <si>
+    <t>10005</t>
+  </si>
+  <si>
     <t>10001;10006</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
     <t>奖励6</t>
   </si>
   <si>
+    <t>10006</t>
+  </si>
+  <si>
     <t>10001;10007</t>
   </si>
   <si>
+    <t>7</t>
+  </si>
+  <si>
     <t>奖励7</t>
   </si>
   <si>
+    <t>10007</t>
+  </si>
+  <si>
     <t>10001;10008</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>奖励8</t>
   </si>
   <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>10008</t>
+  </si>
+  <si>
     <t>10001;10009</t>
   </si>
   <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>奖励9</t>
   </si>
   <si>
+    <t>300</t>
+  </si>
+  <si>
+    <t>10009</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>奖励10</t>
+  </si>
+  <si>
+    <t>10000</t>
   </si>
 </sst>
 </file>
@@ -760,197 +841,197 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" applyNumberFormat="1" fontId="4" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" applyNumberFormat="1" fontId="4" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" applyNumberFormat="1" fontId="4" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" applyNumberFormat="1" fontId="4" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" applyNumberFormat="1" fontId="4" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="0" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="0" applyFill="0" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="5" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="6" applyFill="1" borderId="9" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="6" applyFill="1" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="7" applyFill="1" borderId="10" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="0" applyFill="0" borderId="11" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="0" applyFill="0" borderId="12" applyBorder="1" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="23" applyFont="1" fillId="33" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" applyNumberFormat="0" fontId="22" applyFont="1" fillId="34" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="4" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="2" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="3" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="1" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1297,31 +1378,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:O14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9.29090909090909" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.71818181818182" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.0090909090909" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="6" max="6" width="5.57272727272727" style="2" customWidth="1"/>
-    <col min="7" max="7" width="32.5727272727273" style="2" customWidth="1"/>
-    <col min="8" max="8" width="48.1454545454545" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.1454545454545" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.4363636363636" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.8636363636364" style="1" customWidth="1"/>
-    <col min="12" max="12" width="28.0090909090909" style="1" customWidth="1"/>
-    <col min="13" max="13" width="13.0090909090909" style="3" customWidth="1"/>
-    <col min="14" max="14" width="5.14545454545455" style="3" customWidth="1"/>
-    <col min="15" max="36" width="12.4363636363636" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.29090909090909" customWidth="1" style="1"/>
+    <col min="2" max="2" width="6.71818181818182" customWidth="1" style="2"/>
+    <col min="3" max="3" width="12.4363636363636" customWidth="1" style="1"/>
+    <col min="4" max="4" width="11.0090909090909" customWidth="1" style="1"/>
+    <col min="5" max="5" width="12.4363636363636" customWidth="1" style="1"/>
+    <col min="6" max="6" width="5.57272727272727" customWidth="1" style="2"/>
+    <col min="7" max="7" width="32.5727272727273" customWidth="1" style="2"/>
+    <col min="8" max="8" width="48.1454545454545" customWidth="1" style="1"/>
+    <col min="9" max="9" width="13.1454545454545" customWidth="1" style="1"/>
+    <col min="10" max="10" width="12.4363636363636" customWidth="1" style="1"/>
+    <col min="11" max="11" width="17.8636363636364" customWidth="1" style="1"/>
+    <col min="12" max="12" width="28.0090909090909" customWidth="1" style="1"/>
+    <col min="13" max="13" width="13.0090909090909" customWidth="1" style="3"/>
+    <col min="14" max="14" width="5.14545454545455" customWidth="1" style="3"/>
+    <col min="15" max="36" width="12.4363636363636" customWidth="1" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="1:15">
+    <row r="1" ht="21.75" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +1435,7 @@
       <c r="N1" s="10"/>
       <c r="O1" s="11"/>
     </row>
-    <row r="2" ht="21.75" customHeight="1" spans="1:15">
+    <row r="2" ht="21.75" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
@@ -1387,7 +1468,7 @@
       <c r="N2" s="14"/>
       <c r="O2" s="11"/>
     </row>
-    <row r="3" ht="21.75" customHeight="1" spans="1:15">
+    <row r="3" ht="21.75" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
@@ -1410,7 +1491,7 @@
       <c r="N3" s="14"/>
       <c r="O3" s="11"/>
     </row>
-    <row r="4" ht="22.5" customHeight="1" spans="1:15">
+    <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>16</v>
       </c>
@@ -1441,262 +1522,270 @@
       <c r="N4" s="4"/>
       <c r="O4" s="11"/>
     </row>
-    <row r="5" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B5" s="8">
-        <v>1</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1</v>
+    <row r="5" ht="20.25" customHeight="1">
+      <c r="B5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="8">
-        <v>100</v>
-      </c>
-      <c r="G5" s="8">
-        <v>10001</v>
+        <v>25</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>27</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="M5" s="16"/>
       <c r="N5" s="16"/>
     </row>
-    <row r="6" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B6" s="8">
-        <v>2</v>
-      </c>
-      <c r="C6" s="8">
-        <v>2</v>
+    <row r="6" ht="20.25" customHeight="1">
+      <c r="B6" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="8">
-        <v>100</v>
-      </c>
-      <c r="G6" s="8">
-        <v>10002</v>
+        <v>30</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>31</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="M6" s="16"/>
       <c r="N6" s="16"/>
     </row>
-    <row r="7" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B7" s="8">
-        <v>3</v>
-      </c>
-      <c r="C7" s="8">
-        <v>3</v>
+    <row r="7" ht="20.25" customHeight="1">
+      <c r="B7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="8">
-        <v>100</v>
-      </c>
-      <c r="G7" s="8">
-        <v>10003</v>
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B8" s="8">
-        <v>4</v>
-      </c>
-      <c r="C8" s="8">
-        <v>4</v>
+    <row r="8" ht="20.25" customHeight="1">
+      <c r="B8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="8">
-        <v>100</v>
-      </c>
-      <c r="G8" s="8">
-        <v>10004</v>
+        <v>41</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="M8" s="16"/>
       <c r="N8" s="16"/>
     </row>
-    <row r="9" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B9" s="8">
-        <v>5</v>
-      </c>
-      <c r="C9" s="8">
-        <v>5</v>
+    <row r="9" ht="20.25" customHeight="1">
+      <c r="B9" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="8">
-        <v>100</v>
-      </c>
-      <c r="G9" s="8">
-        <v>10005</v>
+        <v>45</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="M9" s="16"/>
       <c r="N9" s="16"/>
     </row>
-    <row r="10" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B10" s="8">
-        <v>6</v>
-      </c>
-      <c r="C10" s="8">
-        <v>6</v>
+    <row r="10" ht="20.25" customHeight="1">
+      <c r="B10" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="8">
-        <v>100</v>
-      </c>
-      <c r="G10" s="8">
-        <v>10006</v>
+        <v>49</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="M10" s="16"/>
       <c r="N10" s="16"/>
     </row>
-    <row r="11" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B11" s="8">
-        <v>7</v>
-      </c>
-      <c r="C11" s="8">
-        <v>7</v>
+    <row r="11" ht="20.25" customHeight="1">
+      <c r="B11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="8">
-        <v>100</v>
-      </c>
-      <c r="G11" s="8">
-        <v>10007</v>
+        <v>53</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="M11" s="16"/>
       <c r="N11" s="16"/>
     </row>
-    <row r="12" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B12" s="8">
-        <v>8</v>
-      </c>
-      <c r="C12" s="8">
-        <v>8</v>
+    <row r="12" ht="20.25" customHeight="1">
+      <c r="B12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="8">
-        <v>200</v>
-      </c>
-      <c r="G12" s="8">
-        <v>10008</v>
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="M12" s="16"/>
       <c r="N12" s="16"/>
     </row>
-    <row r="13" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B13" s="8">
-        <v>9</v>
-      </c>
-      <c r="C13" s="8">
-        <v>9</v>
+    <row r="13" ht="20.25" customHeight="1">
+      <c r="B13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="8">
-        <v>300</v>
-      </c>
-      <c r="G13" s="8">
-        <v>10009</v>
+        <v>62</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="M13" s="16"/>
       <c r="N13" s="16"/>
     </row>
-    <row r="14" ht="20.25" customHeight="1" spans="2:14">
-      <c r="B14" s="8">
-        <v>10</v>
-      </c>
-      <c r="C14" s="8">
-        <v>10</v>
+    <row r="14" ht="20.25" customHeight="1">
+      <c r="B14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>65</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F14" s="8">
-        <v>100</v>
-      </c>
-      <c r="G14" s="8">
-        <v>10000</v>
+        <v>66</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="M14" s="16"/>
       <c r="N14" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells>
     <mergeCell ref="M1:N1"/>
     <mergeCell ref="M2:N2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to AION.CoreGame under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>